--- a/Data/Input_minna_gagnasett.xlsx
+++ b/Data/Input_minna_gagnasett.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\silja\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EE2AB78-BAB2-4E36-B6D4-498D75DF62E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{133114C8-FABA-4496-92DA-746A48FE238D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="1" activeTab="6" xr2:uid="{7CFC1604-4118-4D2C-86E1-DDF4E62B5004}"/>
   </bookViews>
@@ -16,10 +16,11 @@
     <sheet name="Events" sheetId="3" r:id="rId1"/>
     <sheet name="Employees" sheetId="2" r:id="rId2"/>
     <sheet name="DaysOff" sheetId="4" r:id="rId3"/>
-    <sheet name="ScoreKeys" sheetId="7" r:id="rId4"/>
-    <sheet name="SkillsetScores" sheetId="8" r:id="rId5"/>
-    <sheet name="EventTypes" sheetId="5" r:id="rId6"/>
-    <sheet name="Score krass" sheetId="6" r:id="rId7"/>
+    <sheet name="EventReq" sheetId="9" r:id="rId4"/>
+    <sheet name="ScoreKeys" sheetId="7" r:id="rId5"/>
+    <sheet name="SkillsetScores" sheetId="8" r:id="rId6"/>
+    <sheet name="EventTypes" sheetId="5" r:id="rId7"/>
+    <sheet name="Score krass" sheetId="6" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="126">
   <si>
     <t xml:space="preserve">1.5.2024 </t>
   </si>
@@ -410,13 +411,16 @@
     <t>EmpSkillset</t>
   </si>
   <si>
-    <t>bæta við category type?</t>
-  </si>
-  <si>
     <t>Ef þarf skillset 1 en þú ert ekki</t>
   </si>
   <si>
     <t>Ef þarf skillset 3 og þú ert 1 eða 2</t>
+  </si>
+  <si>
+    <t>Req_this_shift</t>
+  </si>
+  <si>
+    <t>Category</t>
   </si>
 </sst>
 </file>
@@ -476,15 +480,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1261,8 +1266,100 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CDBEBCA-9333-4395-841D-0D115A225A6C}">
+  <dimension ref="A1:AG5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="12.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.08984375" customWidth="1"/>
+    <col min="3" max="5" width="10.26953125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:33" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+      <c r="M1" s="3"/>
+      <c r="N1" s="3"/>
+      <c r="O1" s="3"/>
+      <c r="P1" s="3"/>
+      <c r="Q1" s="3"/>
+      <c r="R1" s="3"/>
+      <c r="S1" s="3"/>
+      <c r="T1" s="3"/>
+      <c r="U1" s="3"/>
+      <c r="V1" s="3"/>
+      <c r="W1" s="3"/>
+      <c r="X1" s="3"/>
+      <c r="Y1" s="3"/>
+      <c r="Z1" s="3"/>
+      <c r="AA1" s="3"/>
+      <c r="AB1" s="3"/>
+      <c r="AC1" s="3"/>
+      <c r="AD1" s="3"/>
+      <c r="AE1" s="3"/>
+      <c r="AF1" s="3"/>
+      <c r="AG1" s="3"/>
+    </row>
+    <row r="2" spans="1:33" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3" spans="1:33" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:33" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B4" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="5" spans="1:33" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B5" t="s">
+        <v>106</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE134D07-2ED5-4277-9A21-369947BF3DF7}">
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E36"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="18.26953125" bestFit="1" customWidth="1"/>
@@ -1344,9 +1441,7 @@
       <c r="C7">
         <v>50</v>
       </c>
-      <c r="E7" s="5" t="s">
-        <v>122</v>
-      </c>
+      <c r="E7" s="4"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
@@ -1408,7 +1503,7 @@
         <v>32</v>
       </c>
       <c r="B13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C13">
         <v>20</v>
@@ -1419,7 +1514,7 @@
         <v>32</v>
       </c>
       <c r="B14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C14">
         <v>10</v>
@@ -1430,7 +1525,7 @@
         <v>32</v>
       </c>
       <c r="B15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -1441,10 +1536,10 @@
         <v>32</v>
       </c>
       <c r="B16">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C16">
-        <v>-10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
@@ -1452,10 +1547,10 @@
         <v>32</v>
       </c>
       <c r="B17">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C17">
-        <v>-20</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
@@ -1471,13 +1566,13 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>115</v>
+        <v>32</v>
       </c>
       <c r="B19">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C19">
-        <v>-10</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
@@ -1485,10 +1580,10 @@
         <v>115</v>
       </c>
       <c r="B20">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C20">
-        <v>-20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
@@ -1496,10 +1591,10 @@
         <v>115</v>
       </c>
       <c r="B21">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C21">
-        <v>-40</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
@@ -1507,10 +1602,10 @@
         <v>115</v>
       </c>
       <c r="B22">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C22">
-        <v>-80</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
@@ -1518,33 +1613,32 @@
         <v>115</v>
       </c>
       <c r="B23">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C23">
-        <v>-160</v>
+        <v>-40</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B24">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C24">
-        <v>-1</v>
+        <v>-80</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B25">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C25">
-        <f>+C24*2</f>
-        <v>-2</v>
+        <v>-160</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
@@ -1552,11 +1646,10 @@
         <v>116</v>
       </c>
       <c r="B26">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C26">
-        <f>+C25*2</f>
-        <v>-4</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
@@ -1564,22 +1657,112 @@
         <v>116</v>
       </c>
       <c r="B27">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C27">
         <f>+C26*2</f>
-        <v>-8</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
+        <v>116</v>
+      </c>
+      <c r="B28">
+        <v>3</v>
+      </c>
+      <c r="C28">
+        <f>+C27*2</f>
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>116</v>
+      </c>
+      <c r="B29">
+        <v>4</v>
+      </c>
+      <c r="C29">
+        <f>+C28*2</f>
+        <v>-8</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
         <v>117</v>
       </c>
-      <c r="B28">
-        <v>1</v>
-      </c>
-      <c r="C28">
+      <c r="B30">
+        <v>1</v>
+      </c>
+      <c r="C30">
         <v>-50</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>124</v>
+      </c>
+      <c r="B31">
+        <v>1</v>
+      </c>
+      <c r="C31">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>125</v>
+      </c>
+      <c r="B32">
+        <v>0</v>
+      </c>
+      <c r="C32">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>125</v>
+      </c>
+      <c r="B33">
+        <v>1</v>
+      </c>
+      <c r="C33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>125</v>
+      </c>
+      <c r="B34">
+        <v>2</v>
+      </c>
+      <c r="C34">
+        <v>-20</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>125</v>
+      </c>
+      <c r="B35">
+        <v>3</v>
+      </c>
+      <c r="C35">
+        <v>-60</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>125</v>
+      </c>
+      <c r="B36">
+        <v>4</v>
+      </c>
+      <c r="C36">
+        <v>-100</v>
       </c>
     </row>
   </sheetData>
@@ -1587,7 +1770,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6EC1D4D2-5C1A-491D-B433-41D3ADCB02A2}">
   <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1712,7 +1895,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A60ED287-5985-48C0-88D9-B8B2B82FB872}">
   <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -2098,7 +2281,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C4BFCF1-DD02-4616-AA4A-3FD405A6C41D}">
   <dimension ref="A1:G41"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -2109,11 +2292,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
       <c r="E1" s="2" t="s">
         <v>113</v>
       </c>
@@ -2613,7 +2796,7 @@
         <v>93</v>
       </c>
       <c r="B35" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C35">
         <v>-1000</v>
@@ -2661,7 +2844,7 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B41" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C41">
         <v>-200</v>

--- a/Data/Input_minna_gagnasett.xlsx
+++ b/Data/Input_minna_gagnasett.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\silja\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{133114C8-FABA-4496-92DA-746A48FE238D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2B80EF4-E5DA-41CA-8921-B99158C1D29C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="1" activeTab="6" xr2:uid="{7CFC1604-4118-4D2C-86E1-DDF4E62B5004}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="9780" windowHeight="11370" firstSheet="3" activeTab="3" xr2:uid="{7CFC1604-4118-4D2C-86E1-DDF4E62B5004}"/>
   </bookViews>
   <sheets>
     <sheet name="Events" sheetId="3" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="127">
   <si>
     <t xml:space="preserve">1.5.2024 </t>
   </si>
@@ -421,6 +421,9 @@
   </si>
   <si>
     <t>Category</t>
+  </si>
+  <si>
+    <t>x</t>
   </si>
 </sst>
 </file>
@@ -486,10 +489,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -954,7 +957,7 @@
         <v>1</v>
       </c>
       <c r="J3" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K3" s="1">
         <v>0.66666666666666663</v>
@@ -1282,13 +1285,13 @@
       <c r="B1" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="5" t="s">
         <v>103</v>
       </c>
       <c r="F1" s="3"/>
@@ -1335,6 +1338,9 @@
       <c r="B3" t="s">
         <v>4</v>
       </c>
+      <c r="C3" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="4" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
@@ -2292,11 +2298,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
       <c r="E1" s="2" t="s">
         <v>113</v>
       </c>
